--- a/artfynd/A 3513-2022 artfynd.xlsx
+++ b/artfynd/A 3513-2022 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 3513-2022 artfynd.xlsx
+++ b/artfynd/A 3513-2022 artfynd.xlsx
@@ -2937,7 +2937,7 @@
         <v>107194367</v>
       </c>
       <c r="B21" t="n">
-        <v>5113</v>
+        <v>5166</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2983,10 +2983,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>342601.966762469</v>
+        <v>342602</v>
       </c>
       <c r="R21" t="n">
-        <v>6603915.25001215</v>
+        <v>6603916</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3016,19 +3016,9 @@
           <t>2022-05-20</t>
         </is>
       </c>
-      <c r="Z21" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA21" t="inlineStr">
         <is>
           <t>2022-05-20</t>
-        </is>
-      </c>
-      <c r="AB21" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD21" t="b">

--- a/artfynd/A 3513-2022 artfynd.xlsx
+++ b/artfynd/A 3513-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY22"/>
+  <dimension ref="A1:AY24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1297,10 +1297,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>66538561</v>
+        <v>66538596</v>
       </c>
       <c r="B7" t="n">
-        <v>89967</v>
+        <v>89356</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1309,25 +1309,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1179</v>
+        <v>5447</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Gräddticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Perenniporia subacida</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Peck) Donk</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1341,10 +1341,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>342726.5421703465</v>
+        <v>342860.6811007226</v>
       </c>
       <c r="R7" t="n">
-        <v>6603842.002557977</v>
+        <v>6603936.39573933</v>
       </c>
       <c r="S7" t="n">
         <v>50</v>
@@ -1400,7 +1400,7 @@
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>21365</t>
+          <t>21393</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
@@ -1418,10 +1418,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>66538599</v>
+        <v>66538561</v>
       </c>
       <c r="B8" t="n">
-        <v>89356</v>
+        <v>89967</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1430,25 +1430,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5447</v>
+        <v>1179</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Gräddticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Perenniporia subacida</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Peck) Donk</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1462,10 +1462,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>342641.6995345455</v>
+        <v>342726.5421703465</v>
       </c>
       <c r="R8" t="n">
-        <v>6603844.034311279</v>
+        <v>6603842.002557977</v>
       </c>
       <c r="S8" t="n">
         <v>50</v>
@@ -1521,7 +1521,7 @@
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>21396</t>
+          <t>21365</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
@@ -1539,10 +1539,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>66538584</v>
+        <v>66538599</v>
       </c>
       <c r="B9" t="n">
-        <v>77506</v>
+        <v>89356</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1551,25 +1551,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1583,10 +1583,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>342700.6417248637</v>
+        <v>342641.6995345455</v>
       </c>
       <c r="R9" t="n">
-        <v>6603915.68367683</v>
+        <v>6603844.034311279</v>
       </c>
       <c r="S9" t="n">
         <v>50</v>
@@ -1642,7 +1642,7 @@
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>21383</t>
+          <t>21396</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>
@@ -1653,17 +1653,17 @@
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Via Malin Sahlin</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>66538563</v>
+        <v>66538584</v>
       </c>
       <c r="B10" t="n">
-        <v>89412</v>
+        <v>77506</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1676,21 +1676,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>5442</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1704,10 +1704,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>342600.6832355002</v>
+        <v>342700.6417248637</v>
       </c>
       <c r="R10" t="n">
-        <v>6603836.107750163</v>
+        <v>6603915.68367683</v>
       </c>
       <c r="S10" t="n">
         <v>50</v>
@@ -1752,11 +1752,6 @@
           <t>00:00</t>
         </is>
       </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>På mosse</t>
-        </is>
-      </c>
       <c r="AD10" t="b">
         <v>0</v>
       </c>
@@ -1768,7 +1763,7 @@
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>21366</t>
+          <t>21383</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
@@ -1779,17 +1774,17 @@
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Via Malin Sahlin</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>66538598</v>
+        <v>66538563</v>
       </c>
       <c r="B11" t="n">
-        <v>89356</v>
+        <v>89412</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1798,25 +1793,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>5447</v>
+        <v>5442</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1830,10 +1825,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>342659.7183772394</v>
+        <v>342600.6832355002</v>
       </c>
       <c r="R11" t="n">
-        <v>6603825.003002927</v>
+        <v>6603836.107750163</v>
       </c>
       <c r="S11" t="n">
         <v>50</v>
@@ -1878,6 +1873,11 @@
           <t>00:00</t>
         </is>
       </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>På mosse</t>
+        </is>
+      </c>
       <c r="AD11" t="b">
         <v>0</v>
       </c>
@@ -1889,7 +1889,7 @@
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>21395</t>
+          <t>21366</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>
@@ -1907,53 +1907,57 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>56152128</v>
+        <v>66538574</v>
       </c>
       <c r="B12" t="n">
-        <v>96334</v>
+        <v>89406</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
+          <t>Ovaliderad</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220787</v>
+        <v>1204</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Sunnerstetjärn, O om, Vrm</t>
+          <t>Svenskmyrarna, Vrm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>342674.5506541113</v>
+        <v>342860.6811007226</v>
       </c>
       <c r="R12" t="n">
-        <v>6603851.28806659</v>
+        <v>6603936.39573933</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1975,14 +1979,9 @@
           <t>Karlanda</t>
         </is>
       </c>
-      <c r="X12" t="inlineStr">
-        <is>
-          <t>S-Årj-0203</t>
-        </is>
-      </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2015-04-08</t>
+          <t>2012-05-21</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
@@ -1992,7 +1991,7 @@
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2015-04-08</t>
+          <t>2012-05-21</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
@@ -2000,11 +1999,6 @@
           <t>00:00</t>
         </is>
       </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>5 dellokaler. Dellok.1. 6608099 - 1297049; dellok.2. 6608091 - 1297057; dellok.3. 6608094 - 1297079; dellok.4. 6608010 - 1297148; dellok.5. 6608073 - 1297156. Samtliga 10 m noggrannhet.</t>
-        </is>
-      </c>
       <c r="AD12" t="b">
         <v>0</v>
       </c>
@@ -2013,73 +2007,78 @@
       </c>
       <c r="AG12" t="b">
         <v>0</v>
+      </c>
+      <c r="AR12" t="inlineStr">
+        <is>
+          <t>21375</t>
+        </is>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Owe Nilsson</t>
+          <t>Malin Sahlin</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Uno Skog</t>
-        </is>
-      </c>
-      <c r="AY12" t="inlineStr">
-        <is>
-          <t>Floraväkteri Sverige</t>
-        </is>
-      </c>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>55713259</v>
+        <v>66538598</v>
       </c>
       <c r="B13" t="n">
-        <v>96334</v>
+        <v>89356</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
+          <t>Ovaliderad</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Sunnerstetjärn Öster om, Vrm</t>
+          <t>Svenskmyrarna, Vrm</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>342630.983456845</v>
+        <v>342659.7183772394</v>
       </c>
       <c r="R13" t="n">
-        <v>6603891.696532496</v>
+        <v>6603825.003002927</v>
       </c>
       <c r="S13" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2103,7 +2102,7 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2015-04-08</t>
+          <t>2012-05-21</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
@@ -2113,7 +2112,7 @@
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2015-04-08</t>
+          <t>2012-05-21</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
@@ -2129,23 +2128,28 @@
       </c>
       <c r="AG13" t="b">
         <v>0</v>
+      </c>
+      <c r="AR13" t="inlineStr">
+        <is>
+          <t>21395</t>
+        </is>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Uno Skog</t>
+          <t>Malin Sahlin</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Uno Skog</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>55713258</v>
+        <v>56152128</v>
       </c>
       <c r="B14" t="n">
         <v>96334</v>
@@ -2181,14 +2185,14 @@
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Sunnerstetjärn Öster om, Vrm</t>
+          <t>Sunnerstetjärn, O om, Vrm</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>342623.179652232</v>
+        <v>342674.5506541113</v>
       </c>
       <c r="R14" t="n">
-        <v>6603899.638584781</v>
+        <v>6603851.28806659</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2213,6 +2217,11 @@
           <t>Karlanda</t>
         </is>
       </c>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>S-Årj-0203</t>
+        </is>
+      </c>
       <c r="Y14" t="inlineStr">
         <is>
           <t>2015-04-08</t>
@@ -2231,6 +2240,11 @@
       <c r="AB14" t="inlineStr">
         <is>
           <t>00:00</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>5 dellokaler. Dellok.1. 6608099 - 1297049; dellok.2. 6608091 - 1297057; dellok.3. 6608094 - 1297079; dellok.4. 6608010 - 1297148; dellok.5. 6608073 - 1297156. Samtliga 10 m noggrannhet.</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2245,19 +2259,23 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
+          <t>Owe Nilsson</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
           <t>Uno Skog</t>
         </is>
       </c>
-      <c r="AX14" t="inlineStr">
-        <is>
-          <t>Uno Skog</t>
-        </is>
-      </c>
-      <c r="AY14" t="inlineStr"/>
+      <c r="AY14" t="inlineStr">
+        <is>
+          <t>Floraväkteri Sverige</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>55713263</v>
+        <v>55713259</v>
       </c>
       <c r="B15" t="n">
         <v>96334</v>
@@ -2297,10 +2315,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>342723.2378649304</v>
+        <v>342630.983456845</v>
       </c>
       <c r="R15" t="n">
-        <v>6603811.680644982</v>
+        <v>6603891.696532496</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2369,7 +2387,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>55713261</v>
+        <v>55713258</v>
       </c>
       <c r="B16" t="n">
         <v>96334</v>
@@ -2409,10 +2427,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>342730.4602257942</v>
+        <v>342623.179652232</v>
       </c>
       <c r="R16" t="n">
-        <v>6603874.836846268</v>
+        <v>6603899.638584781</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2481,7 +2499,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>55713260</v>
+        <v>55713263</v>
       </c>
       <c r="B17" t="n">
         <v>96334</v>
@@ -2521,10 +2539,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>342652.9823875002</v>
+        <v>342723.2378649304</v>
       </c>
       <c r="R17" t="n">
-        <v>6603894.835864382</v>
+        <v>6603811.680644982</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2593,50 +2611,50 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>107194363</v>
+        <v>55713261</v>
       </c>
       <c r="B18" t="n">
-        <v>89412</v>
+        <v>96334</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Godkänd baserat på observatörens uppgifter</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>5442</v>
+        <v>220787</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Sunnerstetjärnet, Vrm</t>
+          <t>Sunnerstetjärn Öster om, Vrm</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>342587.0804117913</v>
+        <v>342730.4602257942</v>
       </c>
       <c r="R18" t="n">
-        <v>6603827.032220867</v>
+        <v>6603874.836846268</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2663,7 +2681,7 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2022-05-20</t>
+          <t>2015-04-08</t>
         </is>
       </c>
       <c r="Z18" t="inlineStr">
@@ -2673,7 +2691,7 @@
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2022-05-20</t>
+          <t>2015-04-08</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
@@ -2693,62 +2711,62 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Jan Rees</t>
+          <t>Uno Skog</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Jan Rees</t>
+          <t>Uno Skog</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>107194387</v>
+        <v>55713260</v>
       </c>
       <c r="B19" t="n">
-        <v>77506</v>
+        <v>96334</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Godkänd baserat på observatörens uppgifter</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Sunnerstetjärnet, Vrm</t>
+          <t>Sunnerstetjärn Öster om, Vrm</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>342553.223004616</v>
+        <v>342652.9823875002</v>
       </c>
       <c r="R19" t="n">
-        <v>6603868.55784877</v>
+        <v>6603894.835864382</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2775,7 +2793,7 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2022-05-20</t>
+          <t>2015-04-08</t>
         </is>
       </c>
       <c r="Z19" t="inlineStr">
@@ -2785,7 +2803,7 @@
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2022-05-20</t>
+          <t>2015-04-08</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr">
@@ -2805,22 +2823,22 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Jan Rees</t>
+          <t>Uno Skog</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Jan Rees</t>
+          <t>Uno Skog</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>107194370</v>
+        <v>107194363</v>
       </c>
       <c r="B20" t="n">
-        <v>56395</v>
+        <v>89412</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2833,39 +2851,34 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100109</v>
+        <v>5442</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Sunnerstetjärnet, Vrm</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>342651.6567499102</v>
+        <v>342587.0804117913</v>
       </c>
       <c r="R20" t="n">
-        <v>6603936.011968089</v>
+        <v>6603827.032220867</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2934,10 +2947,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>107194367</v>
+        <v>107194387</v>
       </c>
       <c r="B21" t="n">
-        <v>5166</v>
+        <v>77506</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2946,47 +2959,38 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100526</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="J21" t="inlineStr"/>
-      <c r="K21" t="inlineStr"/>
-      <c r="L21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
-      <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Sunnerstetjärnet, Vrm</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>342602</v>
+        <v>342553.223004616</v>
       </c>
       <c r="R21" t="n">
-        <v>6603916</v>
+        <v>6603868.55784877</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3016,18 +3020,27 @@
           <t>2022-05-20</t>
         </is>
       </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>00:00</t>
+        </is>
+      </c>
       <c r="AA21" t="inlineStr">
         <is>
           <t>2022-05-20</t>
         </is>
       </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>00:00</t>
+        </is>
+      </c>
       <c r="AD21" t="b">
         <v>0</v>
       </c>
       <c r="AE21" t="b">
         <v>0</v>
       </c>
-      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
@@ -3046,7 +3059,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>107194365</v>
+        <v>107194370</v>
       </c>
       <c r="B22" t="n">
         <v>56395</v>
@@ -3091,10 +3104,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>342666.8821033178</v>
+        <v>342651.6567499102</v>
       </c>
       <c r="R22" t="n">
-        <v>6603911.006255825</v>
+        <v>6603936.011968089</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3160,6 +3173,235 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>107194367</v>
+      </c>
+      <c r="B23" t="n">
+        <v>5166</v>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>100526</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Bronshjon</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Callidium coriaceum</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr"/>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Sunnerstetjärnet, Vrm</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>342602</v>
+      </c>
+      <c r="R23" t="n">
+        <v>6603916</v>
+      </c>
+      <c r="S23" t="n">
+        <v>10</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Årjäng</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Karlanda</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2022-05-20</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2022-05-20</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF23" t="inlineStr"/>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Jan Rees</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Jan Rees</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>107194365</v>
+      </c>
+      <c r="B24" t="n">
+        <v>56395</v>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Sunnerstetjärnet, Vrm</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>342666.8821033178</v>
+      </c>
+      <c r="R24" t="n">
+        <v>6603911.006255825</v>
+      </c>
+      <c r="S24" t="n">
+        <v>10</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Årjäng</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Karlanda</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2022-05-20</t>
+        </is>
+      </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>00:00</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2022-05-20</t>
+        </is>
+      </c>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>00:00</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Jan Rees</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Jan Rees</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 3513-2022 artfynd.xlsx
+++ b/artfynd/A 3513-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY24"/>
+  <dimension ref="A1:AY25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,60 +675,52 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>55713262</v>
+        <v>66538561</v>
       </c>
       <c r="B2" t="n">
-        <v>56395</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>92522</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>1179</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gräddticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Perenniporia subacida</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+          <t>(Peck) Donk</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Sunnerstetjärn Öster om, Vrm</t>
+          <t>Svenskmyrarna, Vrm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>342723.3494379306</v>
+        <v>342727</v>
       </c>
       <c r="R2" t="n">
-        <v>6603850.766673347</v>
+        <v>6603842</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -752,27 +744,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2015-04-08</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2012-05-21</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2015-04-08</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Spår i form av äldre ringar</t>
+          <t>2012-05-21</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -783,53 +760,53 @@
       </c>
       <c r="AG2" t="b">
         <v>0</v>
+      </c>
+      <c r="AR2" t="inlineStr">
+        <is>
+          <t>21365</t>
+        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Uno Skog</t>
+          <t>Malin Sahlin</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Uno Skog</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>55713266</v>
+        <v>66538574</v>
       </c>
       <c r="B3" t="n">
-        <v>56395</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>91923</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>1204</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -837,26 +814,19 @@
           <t>1</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>obs i häcktid, lämplig biotop</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Sunnerstetjärn Öster om, Vrm</t>
+          <t>Svenskmyrarna, Vrm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>342721.3097317055</v>
+        <v>342861</v>
       </c>
       <c r="R3" t="n">
-        <v>6603789.931361218</v>
+        <v>6603936</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -880,27 +850,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2015-04-08</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2012-05-21</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2015-04-08</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Födosökande högt upp i döende granar</t>
+          <t>2012-05-21</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -911,31 +866,31 @@
       </c>
       <c r="AG3" t="b">
         <v>0</v>
+      </c>
+      <c r="AR3" t="inlineStr">
+        <is>
+          <t>21375</t>
+        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Uno Skog</t>
+          <t>Malin Sahlin</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Uno Skog</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>55713265</v>
+        <v>66538563</v>
       </c>
       <c r="B4" t="n">
-        <v>56395</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>91930</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -943,21 +898,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>5442</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -965,26 +920,19 @@
           <t>1</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>nyligen använt bo</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Sunnerstetjärn Öster om, Vrm</t>
+          <t>Svenskmyrarna, Vrm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>342793.8697822151</v>
+        <v>342601</v>
       </c>
       <c r="R4" t="n">
-        <v>6603834.613982104</v>
+        <v>6603836</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1008,27 +956,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2015-04-08</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2012-05-21</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2015-04-08</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2012-05-21</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Använt bohål i gran. Några år gammalt.</t>
+          <t>På mosse</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1039,73 +977,69 @@
       </c>
       <c r="AG4" t="b">
         <v>0</v>
+      </c>
+      <c r="AR4" t="inlineStr">
+        <is>
+          <t>21366</t>
+        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Uno Skog</t>
+          <t>Malin Sahlin</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Uno Skog</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>66538597</v>
+        <v>107194363</v>
       </c>
       <c r="B5" t="n">
-        <v>89356</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91930</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5447</v>
+        <v>5442</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Svenskmyrarna, Vrm</t>
+          <t>Sunnerstetjärnet, Vrm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>342686.7305658329</v>
+        <v>342587</v>
       </c>
       <c r="R5" t="n">
-        <v>6603826.409530371</v>
+        <v>6603827</v>
       </c>
       <c r="S5" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1129,22 +1063,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2012-05-21</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-05-20</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2012-05-21</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-05-20</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1155,36 +1079,26 @@
       </c>
       <c r="AG5" t="b">
         <v>0</v>
-      </c>
-      <c r="AR5" t="inlineStr">
-        <is>
-          <t>21394</t>
-        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Malin Sahlin</t>
+          <t>Jan Rees</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Jan Rees</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>66538612</v>
+        <v>66538596</v>
       </c>
       <c r="B6" t="n">
-        <v>73631</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91872</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1192,21 +1106,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6426</v>
+        <v>5447</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1220,10 +1134,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>342772.0291799856</v>
+        <v>342861</v>
       </c>
       <c r="R6" t="n">
-        <v>6603908.124636303</v>
+        <v>6603936</v>
       </c>
       <c r="S6" t="n">
         <v>50</v>
@@ -1253,21 +1167,11 @@
           <t>2012-05-21</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2012-05-21</t>
         </is>
       </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
@@ -1279,7 +1183,7 @@
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>21407</t>
+          <t>21393</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -1297,15 +1201,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>66538596</v>
+        <v>66538597</v>
       </c>
       <c r="B7" t="n">
-        <v>89356</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91872</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1341,10 +1240,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>342860.6811007226</v>
+        <v>342687</v>
       </c>
       <c r="R7" t="n">
-        <v>6603936.39573933</v>
+        <v>6603826</v>
       </c>
       <c r="S7" t="n">
         <v>50</v>
@@ -1374,21 +1273,11 @@
           <t>2012-05-21</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2012-05-21</t>
         </is>
       </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
@@ -1400,7 +1289,7 @@
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>21393</t>
+          <t>21394</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
@@ -1418,37 +1307,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>66538561</v>
+        <v>66538598</v>
       </c>
       <c r="B8" t="n">
-        <v>89967</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91872</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1179</v>
+        <v>5447</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Gräddticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Perenniporia subacida</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Peck) Donk</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1462,10 +1346,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>342726.5421703465</v>
+        <v>342660</v>
       </c>
       <c r="R8" t="n">
-        <v>6603842.002557977</v>
+        <v>6603825</v>
       </c>
       <c r="S8" t="n">
         <v>50</v>
@@ -1495,21 +1379,11 @@
           <t>2012-05-21</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2012-05-21</t>
         </is>
       </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
@@ -1521,7 +1395,7 @@
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>21365</t>
+          <t>21395</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
@@ -1542,12 +1416,7 @@
         <v>66538599</v>
       </c>
       <c r="B9" t="n">
-        <v>89356</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91872</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1583,10 +1452,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>342641.6995345455</v>
+        <v>342642</v>
       </c>
       <c r="R9" t="n">
-        <v>6603844.034311279</v>
+        <v>6603844</v>
       </c>
       <c r="S9" t="n">
         <v>50</v>
@@ -1616,19 +1485,9 @@
           <t>2012-05-21</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2012-05-21</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1663,16 +1522,11 @@
         <v>66538584</v>
       </c>
       <c r="B10" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
@@ -1704,10 +1558,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>342700.6417248637</v>
+        <v>342701</v>
       </c>
       <c r="R10" t="n">
-        <v>6603915.68367683</v>
+        <v>6603916</v>
       </c>
       <c r="S10" t="n">
         <v>50</v>
@@ -1737,19 +1591,9 @@
           <t>2012-05-21</t>
         </is>
       </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2012-05-21</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1781,57 +1625,48 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>66538563</v>
+        <v>107194387</v>
       </c>
       <c r="B11" t="n">
-        <v>89412</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>5442</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Svenskmyrarna, Vrm</t>
+          <t>Sunnerstetjärnet, Vrm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>342600.6832355002</v>
+        <v>342553</v>
       </c>
       <c r="R11" t="n">
-        <v>6603836.107750163</v>
+        <v>6603869</v>
       </c>
       <c r="S11" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1855,27 +1690,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2012-05-21</t>
-        </is>
-      </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-05-20</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2012-05-21</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>På mosse</t>
+          <t>2022-05-20</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1886,36 +1706,26 @@
       </c>
       <c r="AG11" t="b">
         <v>0</v>
-      </c>
-      <c r="AR11" t="inlineStr">
-        <is>
-          <t>21366</t>
-        </is>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Malin Sahlin</t>
+          <t>Jan Rees</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Jan Rees</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>66538574</v>
+        <v>66538612</v>
       </c>
       <c r="B12" t="n">
-        <v>89406</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>75428</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1923,21 +1733,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1204</v>
+        <v>6426</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1951,10 +1761,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>342860.6811007226</v>
+        <v>342772</v>
       </c>
       <c r="R12" t="n">
-        <v>6603936.39573933</v>
+        <v>6603908</v>
       </c>
       <c r="S12" t="n">
         <v>50</v>
@@ -1984,21 +1794,11 @@
           <t>2012-05-21</t>
         </is>
       </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2012-05-21</t>
         </is>
       </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD12" t="b">
         <v>0</v>
       </c>
@@ -2010,7 +1810,7 @@
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>21375</t>
+          <t>21407</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>
@@ -2028,57 +1828,55 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>66538598</v>
+        <v>55713262</v>
       </c>
       <c r="B13" t="n">
-        <v>89356</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>5447</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>1</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Svenskmyrarna, Vrm</t>
+          <t>Sunnerstetjärn Öster om, Vrm</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>342659.7183772394</v>
+        <v>342723</v>
       </c>
       <c r="R13" t="n">
-        <v>6603825.003002927</v>
+        <v>6603851</v>
       </c>
       <c r="S13" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2102,22 +1900,17 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2012-05-21</t>
-        </is>
-      </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2015-04-08</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2012-05-21</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2015-04-08</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Spår i form av äldre ringar</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2128,71 +1921,72 @@
       </c>
       <c r="AG13" t="b">
         <v>0</v>
-      </c>
-      <c r="AR13" t="inlineStr">
-        <is>
-          <t>21395</t>
-        </is>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Malin Sahlin</t>
+          <t>Uno Skog</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Uno Skog</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>56152128</v>
+        <v>55713265</v>
       </c>
       <c r="B14" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>nyligen använt bo</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Sunnerstetjärn, O om, Vrm</t>
+          <t>Sunnerstetjärn Öster om, Vrm</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>342674.5506541113</v>
+        <v>342794</v>
       </c>
       <c r="R14" t="n">
-        <v>6603851.28806659</v>
+        <v>6603835</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2217,34 +2011,19 @@
           <t>Karlanda</t>
         </is>
       </c>
-      <c r="X14" t="inlineStr">
-        <is>
-          <t>S-Årj-0203</t>
-        </is>
-      </c>
       <c r="Y14" t="inlineStr">
         <is>
           <t>2015-04-08</t>
         </is>
       </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>2015-04-08</t>
         </is>
       </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>5 dellokaler. Dellok.1. 6608099 - 1297049; dellok.2. 6608091 - 1297057; dellok.3. 6608094 - 1297079; dellok.4. 6608010 - 1297148; dellok.5. 6608073 - 1297156. Samtliga 10 m noggrannhet.</t>
+          <t>Använt bohål i gran. Några år gammalt.</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2259,7 +2038,7 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Owe Nilsson</t>
+          <t>Uno Skog</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
@@ -2267,58 +2046,60 @@
           <t>Uno Skog</t>
         </is>
       </c>
-      <c r="AY14" t="inlineStr">
-        <is>
-          <t>Floraväkteri Sverige</t>
-        </is>
-      </c>
+      <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>55713259</v>
+        <v>55713266</v>
       </c>
       <c r="B15" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>obs i häcktid, lämplig biotop</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Sunnerstetjärn Öster om, Vrm</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>342630.983456845</v>
+        <v>342721</v>
       </c>
       <c r="R15" t="n">
-        <v>6603891.696532496</v>
+        <v>6603790</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2348,19 +2129,14 @@
           <t>2015-04-08</t>
         </is>
       </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>2015-04-08</t>
         </is>
       </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>00:00</t>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Födosökande högt upp i döende granar</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2387,50 +2163,50 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>55713258</v>
+        <v>107194365</v>
       </c>
       <c r="B16" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Sunnerstetjärn Öster om, Vrm</t>
+          <t>Sunnerstetjärnet, Vrm</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>342623.179652232</v>
+        <v>342667</v>
       </c>
       <c r="R16" t="n">
-        <v>6603899.638584781</v>
+        <v>6603911</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2457,22 +2233,12 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2015-04-08</t>
-        </is>
-      </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-05-20</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2015-04-08</t>
-        </is>
-      </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-05-20</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2487,62 +2253,62 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Uno Skog</t>
+          <t>Jan Rees</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Uno Skog</t>
+          <t>Jan Rees</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>55713263</v>
+        <v>107194370</v>
       </c>
       <c r="B17" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Sunnerstetjärn Öster om, Vrm</t>
+          <t>Sunnerstetjärnet, Vrm</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>342723.2378649304</v>
+        <v>342651</v>
       </c>
       <c r="R17" t="n">
-        <v>6603811.680644982</v>
+        <v>6603936</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2569,22 +2335,12 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2015-04-08</t>
-        </is>
-      </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-05-20</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2015-04-08</t>
-        </is>
-      </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-05-20</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2599,62 +2355,66 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Uno Skog</t>
+          <t>Jan Rees</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Uno Skog</t>
+          <t>Jan Rees</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>55713261</v>
+        <v>107194367</v>
       </c>
       <c r="B18" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>5179</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>220787</v>
+        <v>100526</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Sunnerstetjärn Öster om, Vrm</t>
+          <t>Sunnerstetjärnet, Vrm</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>342730.4602257942</v>
+        <v>342602</v>
       </c>
       <c r="R18" t="n">
-        <v>6603874.836846268</v>
+        <v>6603916</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2681,22 +2441,12 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2015-04-08</t>
-        </is>
-      </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-05-20</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2015-04-08</t>
-        </is>
-      </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-05-20</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2705,68 +2455,73 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
+      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Uno Skog</t>
+          <t>Jan Rees</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Uno Skog</t>
+          <t>Jan Rees</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>55713260</v>
+        <v>107194375</v>
       </c>
       <c r="B19" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>57369</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>220787</v>
+        <v>102961</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Drillsnäppa</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Actitis hypoleucos</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Sunnerstetjärn Öster om, Vrm</t>
+          <t>Sunnerstetjärnet, Vrm</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>342652.9823875002</v>
+        <v>342374</v>
       </c>
       <c r="R19" t="n">
-        <v>6603894.835864382</v>
+        <v>6603767</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2793,22 +2548,12 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2015-04-08</t>
-        </is>
-      </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-05-20</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2015-04-08</t>
-        </is>
-      </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-05-20</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2823,62 +2568,57 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Uno Skog</t>
+          <t>Jan Rees</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Uno Skog</t>
+          <t>Jan Rees</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>107194363</v>
+        <v>55713258</v>
       </c>
       <c r="B20" t="n">
-        <v>89412</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>5442</v>
+        <v>220787</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Sunnerstetjärnet, Vrm</t>
+          <t>Sunnerstetjärn Öster om, Vrm</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>342587.0804117913</v>
+        <v>342623</v>
       </c>
       <c r="R20" t="n">
-        <v>6603827.032220867</v>
+        <v>6603900</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2905,22 +2645,12 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2022-05-20</t>
-        </is>
-      </c>
-      <c r="Z20" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2015-04-08</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2022-05-20</t>
-        </is>
-      </c>
-      <c r="AB20" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2015-04-08</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2935,62 +2665,57 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Jan Rees</t>
+          <t>Uno Skog</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Jan Rees</t>
+          <t>Uno Skog</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>107194387</v>
+        <v>55713259</v>
       </c>
       <c r="B21" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Sunnerstetjärnet, Vrm</t>
+          <t>Sunnerstetjärn Öster om, Vrm</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>342553.223004616</v>
+        <v>342631</v>
       </c>
       <c r="R21" t="n">
-        <v>6603868.55784877</v>
+        <v>6603892</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3017,22 +2742,12 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2022-05-20</t>
-        </is>
-      </c>
-      <c r="Z21" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2015-04-08</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2022-05-20</t>
-        </is>
-      </c>
-      <c r="AB21" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2015-04-08</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3047,67 +2762,57 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Jan Rees</t>
+          <t>Uno Skog</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Jan Rees</t>
+          <t>Uno Skog</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>107194370</v>
+        <v>55713260</v>
       </c>
       <c r="B22" t="n">
-        <v>56395</v>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Sunnerstetjärnet, Vrm</t>
+          <t>Sunnerstetjärn Öster om, Vrm</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>342651.6567499102</v>
+        <v>342653</v>
       </c>
       <c r="R22" t="n">
-        <v>6603936.011968089</v>
+        <v>6603895</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3134,22 +2839,12 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2022-05-20</t>
-        </is>
-      </c>
-      <c r="Z22" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2015-04-08</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2022-05-20</t>
-        </is>
-      </c>
-      <c r="AB22" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2015-04-08</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3164,71 +2859,57 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Jan Rees</t>
+          <t>Uno Skog</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Jan Rees</t>
+          <t>Uno Skog</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>107194367</v>
+        <v>55713261</v>
       </c>
       <c r="B23" t="n">
-        <v>5166</v>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100526</v>
+        <v>220787</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="J23" t="inlineStr"/>
-      <c r="K23" t="inlineStr"/>
-      <c r="L23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
-      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Sunnerstetjärnet, Vrm</t>
+          <t>Sunnerstetjärn Öster om, Vrm</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>342602</v>
+        <v>342730</v>
       </c>
       <c r="R23" t="n">
-        <v>6603916</v>
+        <v>6603875</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3255,12 +2936,12 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2022-05-20</t>
+          <t>2015-04-08</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2022-05-20</t>
+          <t>2015-04-08</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3269,74 +2950,63 @@
       <c r="AE23" t="b">
         <v>0</v>
       </c>
-      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Jan Rees</t>
+          <t>Uno Skog</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Jan Rees</t>
+          <t>Uno Skog</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>107194365</v>
+        <v>55713263</v>
       </c>
       <c r="B24" t="n">
-        <v>56395</v>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Sunnerstetjärnet, Vrm</t>
+          <t>Sunnerstetjärn Öster om, Vrm</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>342666.8821033178</v>
+        <v>342723</v>
       </c>
       <c r="R24" t="n">
-        <v>6603911.006255825</v>
+        <v>6603812</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3363,22 +3033,12 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2022-05-20</t>
-        </is>
-      </c>
-      <c r="Z24" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2015-04-08</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2022-05-20</t>
-        </is>
-      </c>
-      <c r="AB24" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2015-04-08</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3393,15 +3053,126 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Jan Rees</t>
+          <t>Uno Skog</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Jan Rees</t>
+          <t>Uno Skog</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>56152128</v>
+      </c>
+      <c r="B25" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Sunnerstetjärn, O om, Vrm</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>342675</v>
+      </c>
+      <c r="R25" t="n">
+        <v>6603851</v>
+      </c>
+      <c r="S25" t="n">
+        <v>10</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Årjäng</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Karlanda</t>
+        </is>
+      </c>
+      <c r="X25" t="inlineStr">
+        <is>
+          <t>S-Årj-0203</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2015-04-08</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2015-04-08</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>5 dellokaler. Dellok.1. 6608099 - 1297049; dellok.2. 6608091 - 1297057; dellok.3. 6608094 - 1297079; dellok.4. 6608010 - 1297148; dellok.5. 6608073 - 1297156. Samtliga 10 m noggrannhet.</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Owe Nilsson</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Uno Skog</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr">
+        <is>
+          <t>Floraväkteri Sverige</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
